--- a/DateBase/orders/Nha Thu_2026-4-2.xlsx
+++ b/DateBase/orders/Nha Thu_2026-4-2.xlsx
@@ -523,6 +523,9 @@
       <c r="C11" t="str">
         <v>246_多头蓝莓_Blueberry Spray_Rosa rugosa Thunb._10stems</v>
       </c>
+      <c r="F11" t="str">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -581,7 +584,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>016051010596580</v>
+        <v>016051010596586</v>
       </c>
     </row>
   </sheetData>
